--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ96"/>
+  <dimension ref="A1:AZ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10211,10 +10211,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119677118</v>
+        <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>97977</v>
+        <v>106479</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10222,33 +10222,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221944</v>
+        <v>221725</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>855491</v>
+        <v>855322</v>
       </c>
       <c r="R94" t="n">
-        <v>7477890</v>
+        <v>7478122</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10272,12 +10276,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10286,7 +10290,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10304,16 +10307,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119677118</t>
+          <t>https://artportalen.se/Sighting/136866910</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134119807</v>
+        <v>119677118</v>
       </c>
       <c r="B95" t="n">
-        <v>99001</v>
+        <v>97977</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10321,37 +10324,33 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>223049</v>
+        <v>221944</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>855268</v>
+        <v>855491</v>
       </c>
       <c r="R95" t="n">
-        <v>7477876</v>
+        <v>7477890</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10375,12 +10374,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10389,6 +10388,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10406,13 +10406,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119807</t>
+          <t>https://artportalen.se/Sighting/119677118</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134119808</v>
+        <v>134119807</v>
       </c>
       <c r="B96" t="n">
         <v>99001</v>
@@ -10447,10 +10447,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855303</v>
+        <v>855268</v>
       </c>
       <c r="R96" t="n">
-        <v>7477930</v>
+        <v>7477876</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10507,6 +10507,108 @@
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119807</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>134119808</v>
+      </c>
+      <c r="B97" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>855303</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7477930</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134119808</t>
         </is>
@@ -10609,6 +10711,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106479</v>
+        <v>106485</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106485</v>
+        <v>106487</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106487</v>
+        <v>106488</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106488</v>
+        <v>106494</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106494</v>
+        <v>106498</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106498</v>
+        <v>106500</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106502</v>
+        <v>106515</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106517</v>
+        <v>106521</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106521</v>
+        <v>106541</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106541</v>
+        <v>106542</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106542</v>
+        <v>106547</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106547</v>
+        <v>106550</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106550</v>
+        <v>106556</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10214,7 +10214,7 @@
         <v>136866910</v>
       </c>
       <c r="B94" t="n">
-        <v>106557</v>
+        <v>106569</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
